--- a/data/pack/us/azucar.xlsx
+++ b/data/pack/us/azucar.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -12657,7 +12657,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -13152,7 +13152,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -14857,7 +14857,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -14967,7 +14967,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -15297,7 +15297,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -16012,7 +16012,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -16067,7 +16067,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -16452,7 +16452,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -16672,7 +16672,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -17057,7 +17057,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -17167,7 +17167,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -17332,7 +17332,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -17882,7 +17882,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -17992,7 +17992,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -18047,7 +18047,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -18157,7 +18157,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -18267,7 +18267,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -18322,7 +18322,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -18377,7 +18377,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -18542,7 +18542,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -18652,7 +18652,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -18707,7 +18707,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -18762,7 +18762,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -18872,7 +18872,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -18927,7 +18927,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -19147,7 +19147,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -19257,7 +19257,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -19312,7 +19312,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -19477,7 +19477,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -19697,7 +19697,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -19807,7 +19807,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -20027,7 +20027,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -20137,7 +20137,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -20302,7 +20302,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -20357,7 +20357,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -20467,7 +20467,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -20577,7 +20577,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -20687,7 +20687,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -20852,7 +20852,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -20907,7 +20907,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -21127,7 +21127,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -21182,7 +21182,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -21237,7 +21237,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -21292,7 +21292,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -21347,7 +21347,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -21622,7 +21622,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -21677,7 +21677,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -21732,7 +21732,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -21897,7 +21897,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -22007,7 +22007,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -22062,7 +22062,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -22117,7 +22117,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -22172,7 +22172,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -22227,7 +22227,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -22282,7 +22282,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -22337,7 +22337,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -22447,7 +22447,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -22502,7 +22502,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -22612,7 +22612,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -22667,7 +22667,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -22832,7 +22832,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -22887,7 +22887,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -22942,7 +22942,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -23162,7 +23162,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -23327,7 +23327,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -23437,7 +23437,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -23712,7 +23712,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -23767,7 +23767,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -23877,7 +23877,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -23987,7 +23987,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -24042,7 +24042,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -24152,7 +24152,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -24207,7 +24207,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -24262,7 +24262,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -24317,7 +24317,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -24372,7 +24372,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -24592,7 +24592,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -24647,7 +24647,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -24702,7 +24702,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -24757,7 +24757,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -24812,7 +24812,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -24867,7 +24867,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -24922,7 +24922,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -24977,7 +24977,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -25032,7 +25032,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -25087,7 +25087,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -25142,7 +25142,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -25307,7 +25307,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -25417,7 +25417,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -25472,7 +25472,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -25582,7 +25582,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -25637,7 +25637,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -25747,7 +25747,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -25857,7 +25857,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -25912,7 +25912,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -25967,7 +25967,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -26077,7 +26077,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -26132,7 +26132,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -26187,7 +26187,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -26242,7 +26242,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -26407,7 +26407,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -26462,7 +26462,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -26517,7 +26517,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -26627,7 +26627,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -26682,7 +26682,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -26792,7 +26792,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -26847,7 +26847,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -26902,7 +26902,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -26957,7 +26957,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -27012,7 +27012,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -27067,7 +27067,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -27122,7 +27122,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -27177,7 +27177,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -27232,7 +27232,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -27507,7 +27507,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -27562,7 +27562,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -27617,7 +27617,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -27782,7 +27782,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -27837,7 +27837,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -27892,7 +27892,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -27947,7 +27947,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -28002,7 +28002,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -28057,7 +28057,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -28167,7 +28167,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -28222,7 +28222,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -28277,7 +28277,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -28332,7 +28332,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -28387,7 +28387,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -28442,7 +28442,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -28607,7 +28607,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -28662,7 +28662,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -28717,7 +28717,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -28772,7 +28772,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -28827,7 +28827,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -28882,7 +28882,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -28992,7 +28992,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -29047,7 +29047,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -29157,7 +29157,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -29212,7 +29212,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -29267,7 +29267,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -29322,7 +29322,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -29377,7 +29377,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -29432,7 +29432,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -29487,7 +29487,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -29542,7 +29542,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -29652,7 +29652,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -29762,7 +29762,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -29817,7 +29817,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -29872,7 +29872,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -29927,7 +29927,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -29982,7 +29982,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -30037,7 +30037,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -30092,7 +30092,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -30147,7 +30147,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -30202,7 +30202,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -30257,7 +30257,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -30312,7 +30312,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -30367,7 +30367,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -30422,7 +30422,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -30477,7 +30477,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -30532,7 +30532,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -30587,7 +30587,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -30642,7 +30642,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -30752,7 +30752,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -30807,7 +30807,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -30862,7 +30862,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -30917,7 +30917,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -30972,7 +30972,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -31027,7 +31027,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -31082,7 +31082,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -31137,7 +31137,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -31192,7 +31192,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -31247,7 +31247,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -31302,7 +31302,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -31357,7 +31357,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -31412,7 +31412,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -31467,7 +31467,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -31522,7 +31522,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -31577,7 +31577,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -31632,7 +31632,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -31687,7 +31687,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -31742,7 +31742,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -31797,7 +31797,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -31852,7 +31852,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -31962,7 +31962,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -32017,7 +32017,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -32072,7 +32072,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -32127,7 +32127,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -32182,7 +32182,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -32237,7 +32237,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -32292,7 +32292,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -32347,7 +32347,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -32402,7 +32402,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -32457,7 +32457,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -32512,7 +32512,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -32567,7 +32567,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -32622,7 +32622,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -32677,7 +32677,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -32732,7 +32732,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -32787,7 +32787,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -32842,7 +32842,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -32897,7 +32897,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -32952,7 +32952,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -33007,7 +33007,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -33117,7 +33117,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -33172,7 +33172,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -33227,7 +33227,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -33282,7 +33282,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -33337,7 +33337,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -33392,7 +33392,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -33447,7 +33447,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -33557,7 +33557,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -33667,7 +33667,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -33722,7 +33722,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -33777,7 +33777,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -33832,7 +33832,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -33887,7 +33887,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -33942,7 +33942,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -33997,7 +33997,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -34107,7 +34107,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -34162,7 +34162,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -34217,7 +34217,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -34272,7 +34272,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -34327,7 +34327,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -34382,7 +34382,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -34437,7 +34437,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -34492,7 +34492,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -34547,7 +34547,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -34602,7 +34602,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -34712,7 +34712,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -34767,7 +34767,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -34822,7 +34822,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -34877,7 +34877,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -34932,7 +34932,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -34987,7 +34987,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -35042,7 +35042,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -35097,7 +35097,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -35152,7 +35152,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -35207,7 +35207,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -35262,7 +35262,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -35317,7 +35317,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -35372,7 +35372,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -35427,7 +35427,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -35482,7 +35482,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -35537,7 +35537,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -35647,7 +35647,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -35757,7 +35757,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -35812,7 +35812,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -35867,7 +35867,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -35922,7 +35922,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -35977,7 +35977,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -36032,7 +36032,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -36087,7 +36087,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -36142,7 +36142,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -36197,7 +36197,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -36252,7 +36252,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -36307,7 +36307,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -36362,7 +36362,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -36472,7 +36472,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -36527,7 +36527,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -36582,7 +36582,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -36637,7 +36637,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -36692,7 +36692,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -36747,7 +36747,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -36802,7 +36802,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -36857,7 +36857,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -36967,7 +36967,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -37022,7 +37022,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -37077,7 +37077,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -37132,7 +37132,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -37187,7 +37187,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -37242,7 +37242,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -37297,7 +37297,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -37352,7 +37352,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -37407,7 +37407,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -37462,7 +37462,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -37517,7 +37517,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -37572,7 +37572,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -37627,7 +37627,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -37682,7 +37682,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -37737,7 +37737,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -37792,7 +37792,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -37847,7 +37847,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -37902,7 +37902,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -37957,7 +37957,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -38012,7 +38012,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -38067,7 +38067,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -38122,7 +38122,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -38177,7 +38177,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -38232,7 +38232,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -38287,7 +38287,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -38342,7 +38342,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -38397,7 +38397,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -38452,7 +38452,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -38507,7 +38507,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -38562,7 +38562,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -38617,7 +38617,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -38672,7 +38672,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -38727,7 +38727,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -38782,7 +38782,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -38837,7 +38837,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -38892,7 +38892,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -38947,7 +38947,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -39002,7 +39002,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -39057,7 +39057,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -39112,7 +39112,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -39167,7 +39167,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -39222,7 +39222,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -39277,7 +39277,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -39332,7 +39332,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -39442,7 +39442,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -39497,7 +39497,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -39552,7 +39552,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -39607,7 +39607,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -39662,7 +39662,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -39717,7 +39717,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -39772,7 +39772,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -39827,7 +39827,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -39882,7 +39882,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -39937,7 +39937,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -40047,7 +40047,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -40102,7 +40102,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -40157,7 +40157,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -40212,7 +40212,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -40267,7 +40267,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -40322,7 +40322,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -40432,7 +40432,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -40487,7 +40487,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -40542,7 +40542,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -40597,7 +40597,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -40652,7 +40652,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -40762,7 +40762,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -40872,7 +40872,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -40927,7 +40927,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -40982,7 +40982,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -41037,7 +41037,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -41092,7 +41092,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -41147,7 +41147,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -41202,7 +41202,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -41257,7 +41257,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -41312,7 +41312,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -41367,7 +41367,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -41422,7 +41422,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -41477,7 +41477,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -41587,7 +41587,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -41642,7 +41642,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -41697,7 +41697,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -41752,7 +41752,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -41807,7 +41807,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -41862,7 +41862,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -41917,7 +41917,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -41972,7 +41972,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -42027,7 +42027,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -42082,7 +42082,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -42137,7 +42137,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -42192,7 +42192,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -42247,7 +42247,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -42302,7 +42302,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -42357,7 +42357,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -42412,7 +42412,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -42467,7 +42467,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -42522,7 +42522,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -42577,7 +42577,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -42632,7 +42632,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -42687,7 +42687,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -42742,7 +42742,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -42797,7 +42797,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -42852,7 +42852,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -42907,7 +42907,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -42962,7 +42962,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -43017,7 +43017,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -43072,7 +43072,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -43127,7 +43127,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -43182,7 +43182,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -43237,7 +43237,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -43347,7 +43347,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -43402,7 +43402,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -43457,7 +43457,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -43512,7 +43512,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -43567,7 +43567,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -43677,7 +43677,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -43732,7 +43732,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -43897,7 +43897,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -43952,7 +43952,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -44007,7 +44007,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -44062,7 +44062,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -44117,7 +44117,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -44172,7 +44172,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -44227,7 +44227,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -44282,7 +44282,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>azucar</t>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -44355,7 +44355,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>azucar (azucar)</t>
+          <t>Azúcar (azucar)</t>
         </is>
       </c>
     </row>
@@ -44367,7 +44367,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US · EE. UU.</t>
         </is>
       </c>
     </row>
@@ -44377,7 +44377,11 @@
           <t>Descripcion del dato</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>USDA ERS, Sugar and Sweeteners Yearbook, table 5: wholesale refined beet sugar price, Midwest markets, bulk, monthly average; USD/lb (ERS publishes cents/lb). Wholesale, not retail; the EU figure is the average ex-factory white sugar price.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
